--- a/data/信用债发行汇总_2026-09-11.xlsx
+++ b/data/信用债发行汇总_2026-09-11.xlsx
@@ -1003,7 +1003,9 @@
           <t>1.60 ~ 2.40</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr"/>
+      <c r="H2" s="3" t="n">
+        <v>1.94</v>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>云南省能源集团有限公司</t>
@@ -11215,7 +11217,9 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>2.34</v>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>肥城市建投产业投资集团有限公司</t>
@@ -11400,7 +11404,9 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="H3" s="2" t="n">
+        <v>2.25</v>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>成都天府大港集团有限公司</t>
@@ -11577,7 +11583,9 @@
           <t>1.80 ~ 2.60</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="H4" s="2" t="n">
+        <v>2.2</v>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>济南产业发展投资集团有限公司</t>
@@ -11758,7 +11766,9 @@
           <t>1.90 ~ 2.50</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="2" t="n">
+        <v>2.14</v>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>天津渤海国有资产经营管理有限公司</t>
@@ -11937,7 +11947,9 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="2" t="n">
+        <v>2.18</v>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>许昌市投资集团有限公司</t>
@@ -12124,7 +12136,9 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="2" t="n">
+        <v>2.03</v>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>中铁十局集团有限公司</t>
@@ -13049,7 +13063,9 @@
           <t>1.90 ~ 2.30</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr"/>
+      <c r="H12" s="2" t="n">
+        <v>2.08</v>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>张家港市城市投资发展集团有限公司</t>
@@ -13234,7 +13250,9 @@
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr"/>
+      <c r="H13" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
           <t>江苏润城城市投资控股集团有限公司</t>
@@ -13586,7 +13604,9 @@
           <t>1.65 ~ 2.05</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="H15" s="2" t="n">
+        <v>1.87</v>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
           <t>广西绿城水务集团股份有限公司</t>
@@ -13769,7 +13789,9 @@
           <t>1.60 ~ 2.40</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="2" t="n">
+        <v>1.94</v>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>云南省能源集团有限公司</t>
@@ -13952,7 +13974,9 @@
           <t>1.70 ~ 2.30</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="2" t="n">
+        <v>1.95</v>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
           <t>福建省德化县矿产工业总公司</t>
@@ -16144,7 +16168,9 @@
           <t>1.84 ~ 2.14</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="H29" s="2" t="n">
+        <v>2.14</v>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
           <t>安徽省皖能股份有限公司</t>
@@ -20359,63 +20385,63 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>09-07 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>26建城01</t>
+          <t>26湖州银行永续债01</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>283858.SH</t>
+          <t>242680044.IB</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
+          <t>1.90 ~ 2.60</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>建湖县城市建设投资集团有限公司</t>
+          <t>湖州银行股份有限公司</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>26建湖城投PPN003</t>
+          <t>25湖州银行永续债01</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>4.97Y</t>
+          <t>4.19Y+N</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2.1973</t>
+          <t>2.1548</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -20425,19 +20451,23 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="inlineStr"/>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司,东吴证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr"/>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行次级债券</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -20447,17 +20477,17 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>建湖县城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>湖州银行股份有限公司2026年无固定期限资本债券</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -20468,12 +20498,12 @@
       <c r="Z52" s="2" t="inlineStr"/>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -20483,32 +20513,32 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AE52" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF52" s="2" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AG52" s="2" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AH52" s="2" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AI52" s="2" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AJ52" s="2" t="inlineStr"/>
@@ -20519,12 +20549,12 @@
       </c>
       <c r="AL52" s="2" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AM52" s="2" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>其他一级资本工具</t>
         </is>
       </c>
       <c r="AN52" s="2" t="inlineStr">
@@ -20542,63 +20572,63 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-07 19:00</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>26湖州银行永续债01</t>
+          <t>26建城01</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>242680044.IB</t>
+          <t>283858.SH</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.60</t>
+          <t>1.70 ~ 2.50</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>湖州银行股份有限公司</t>
+          <t>建湖县城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>25湖州银行永续债01</t>
+          <t>26建湖城投PPN003</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>4.19Y+N</t>
+          <t>4.97Y</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>2.1548</t>
+          <t>2.1973</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -20608,23 +20638,19 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
           <t>AA</t>
         </is>
       </c>
+      <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>长城证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr"/>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>商业银行次级债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -20634,17 +20660,17 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>湖州银行股份有限公司2026年无固定期限资本债券</t>
+          <t>建湖县城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -20655,12 +20681,12 @@
       <c r="Z53" s="2" t="inlineStr"/>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -20670,32 +20696,32 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AE53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF53" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AG53" s="2" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AH53" s="2" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AI53" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AJ53" s="2" t="inlineStr"/>
@@ -20706,12 +20732,12 @@
       </c>
       <c r="AL53" s="2" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AM53" s="2" t="inlineStr">
         <is>
-          <t>其他一级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AN53" s="2" t="inlineStr">
